--- a/storage/inputs/excel/FX4PD.xlsx
+++ b/storage/inputs/excel/FX4PD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WADL6U3\.000 - Projetos\auto-line-feeding\backend\core\storage\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WADL6U3\.000 - Projetos\auto-line-feeding\backend\core\storage\inputs\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33397400-346F-418D-A694-71ED545D7C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C85056-0428-4B58-B183-8BFC900D7B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="332">
   <si>
     <t>CSD-Class 0.0 - max 90 days, Classification: internal, Version: 51_20260205_000424, RequestId: d6fff8f8-1100-43de-b3d9-5bbd1b3c55c3, Creation time: 2026-02-05_11-58-40</t>
   </si>
@@ -1043,10 +1043,7 @@
     <t>[5120260647672, 5120260650123, 5120260660056, 5120260637674, 5120260637770, 5120260660012, 5120260660062]</t>
   </si>
   <si>
-    <t>5120260747693</t>
-  </si>
-  <si>
-    <t>5120260837681</t>
+    <t>5120261037056</t>
   </si>
 </sst>
 </file>
@@ -1523,7 +1520,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
@@ -1601,7 +1598,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
@@ -1653,7 +1650,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
@@ -1705,7 +1702,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
@@ -1783,7 +1780,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
@@ -1835,7 +1832,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B16" t="s">
         <v>28</v>
@@ -1887,7 +1884,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
@@ -1965,7 +1962,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
@@ -2017,7 +2014,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -2069,7 +2066,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B25" t="s">
         <v>37</v>
@@ -2147,7 +2144,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B28" t="s">
         <v>40</v>
@@ -2199,7 +2196,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s">
         <v>42</v>
@@ -2251,7 +2248,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B32" t="s">
         <v>44</v>
@@ -2329,7 +2326,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
@@ -2381,7 +2378,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s">
         <v>49</v>
@@ -2433,7 +2430,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
@@ -2511,7 +2508,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
@@ -2563,7 +2560,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s">
         <v>56</v>
@@ -2615,7 +2612,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B46" t="s">
         <v>58</v>
@@ -2693,7 +2690,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s">
         <v>61</v>
@@ -2745,7 +2742,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s">
         <v>63</v>
@@ -2797,7 +2794,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s">
         <v>65</v>
@@ -2875,7 +2872,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B56" t="s">
         <v>68</v>
@@ -2927,7 +2924,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s">
         <v>70</v>
@@ -2979,7 +2976,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s">
         <v>72</v>
@@ -3057,7 +3054,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B63" t="s">
         <v>75</v>
@@ -3109,7 +3106,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B65" t="s">
         <v>77</v>
@@ -3161,7 +3158,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B67" t="s">
         <v>79</v>
@@ -3239,7 +3236,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B70" t="s">
         <v>82</v>
@@ -3291,7 +3288,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B72" t="s">
         <v>84</v>
@@ -3343,7 +3340,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B74" t="s">
         <v>86</v>
@@ -3421,7 +3418,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
         <v>89</v>
@@ -3473,7 +3470,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s">
         <v>91</v>
@@ -3525,7 +3522,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B81" t="s">
         <v>93</v>
@@ -3603,7 +3600,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B84" t="s">
         <v>96</v>
@@ -3655,7 +3652,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B86" t="s">
         <v>98</v>
@@ -3707,7 +3704,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B88" t="s">
         <v>100</v>
@@ -3785,7 +3782,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B91" t="s">
         <v>103</v>
@@ -3837,7 +3834,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B93" t="s">
         <v>105</v>
@@ -3889,7 +3886,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B95" t="s">
         <v>107</v>
@@ -3967,7 +3964,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s">
         <v>110</v>
@@ -4019,7 +4016,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B100" t="s">
         <v>112</v>
@@ -4071,7 +4068,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B102" t="s">
         <v>114</v>
@@ -4149,7 +4146,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s">
         <v>117</v>
@@ -4201,7 +4198,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B107" t="s">
         <v>119</v>
@@ -4253,7 +4250,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B109" t="s">
         <v>121</v>
@@ -4331,7 +4328,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B112" t="s">
         <v>124</v>
@@ -4383,7 +4380,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B114" t="s">
         <v>126</v>
@@ -4435,7 +4432,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B116" t="s">
         <v>128</v>
@@ -4513,7 +4510,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B119" t="s">
         <v>131</v>
@@ -4565,7 +4562,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B121" t="s">
         <v>133</v>
@@ -4617,7 +4614,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B123" t="s">
         <v>135</v>
@@ -4695,7 +4692,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B126" t="s">
         <v>138</v>
@@ -4747,7 +4744,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B128" t="s">
         <v>140</v>
@@ -4799,7 +4796,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B130" t="s">
         <v>142</v>
@@ -4877,7 +4874,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B133" t="s">
         <v>145</v>
@@ -4929,7 +4926,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B135" t="s">
         <v>147</v>
@@ -4981,7 +4978,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B137" t="s">
         <v>149</v>
@@ -5059,7 +5056,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B140" t="s">
         <v>153</v>
@@ -5111,7 +5108,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B142" t="s">
         <v>155</v>
@@ -5163,7 +5160,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B144" t="s">
         <v>157</v>
@@ -5241,7 +5238,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B147" t="s">
         <v>160</v>
@@ -5293,7 +5290,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B149" t="s">
         <v>162</v>
@@ -5345,7 +5342,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B151" t="s">
         <v>164</v>
@@ -5423,7 +5420,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B154" t="s">
         <v>167</v>
@@ -5475,7 +5472,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B156" t="s">
         <v>169</v>
@@ -5527,7 +5524,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B158" t="s">
         <v>171</v>
@@ -5605,7 +5602,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B161" t="s">
         <v>174</v>
@@ -5657,7 +5654,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B163" t="s">
         <v>176</v>
@@ -5709,7 +5706,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B165" t="s">
         <v>178</v>
@@ -5787,7 +5784,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B168" t="s">
         <v>181</v>
@@ -5839,7 +5836,7 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B170" t="s">
         <v>183</v>
@@ -5891,7 +5888,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B172" t="s">
         <v>185</v>
@@ -5969,7 +5966,7 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B175" t="s">
         <v>188</v>
@@ -6021,7 +6018,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B177" t="s">
         <v>190</v>
@@ -6073,7 +6070,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B179" t="s">
         <v>192</v>
@@ -6151,7 +6148,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B182" t="s">
         <v>195</v>
@@ -6203,7 +6200,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B184" t="s">
         <v>197</v>
@@ -6255,7 +6252,7 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B186" t="s">
         <v>199</v>
@@ -6333,7 +6330,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B189" t="s">
         <v>202</v>
@@ -6385,7 +6382,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B191" t="s">
         <v>204</v>
@@ -6437,7 +6434,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B193" t="s">
         <v>206</v>
@@ -6515,7 +6512,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B196" t="s">
         <v>209</v>
@@ -6567,7 +6564,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B198" t="s">
         <v>211</v>
@@ -6619,7 +6616,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B200" t="s">
         <v>213</v>
@@ -6697,7 +6694,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B203" t="s">
         <v>216</v>
@@ -6749,7 +6746,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B205" t="s">
         <v>218</v>
@@ -6801,7 +6798,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B207" t="s">
         <v>220</v>
@@ -6879,7 +6876,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B210" t="s">
         <v>223</v>
@@ -6931,7 +6928,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B212" t="s">
         <v>225</v>
@@ -6983,7 +6980,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B214" t="s">
         <v>227</v>
@@ -7061,7 +7058,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B217" t="s">
         <v>230</v>
@@ -7113,7 +7110,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B219" t="s">
         <v>232</v>
@@ -7165,7 +7162,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B221" t="s">
         <v>234</v>
@@ -7243,7 +7240,7 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B224" t="s">
         <v>237</v>
@@ -7295,7 +7292,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B226" t="s">
         <v>239</v>
@@ -7347,7 +7344,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B228" t="s">
         <v>241</v>
@@ -7425,7 +7422,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B231" t="s">
         <v>244</v>
@@ -7477,7 +7474,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B233" t="s">
         <v>246</v>
@@ -7529,7 +7526,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B235" t="s">
         <v>248</v>
@@ -7607,7 +7604,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B238" t="s">
         <v>251</v>
@@ -7659,7 +7656,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B240" t="s">
         <v>253</v>
@@ -7711,7 +7708,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B242" t="s">
         <v>255</v>
@@ -7789,7 +7786,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B245" t="s">
         <v>258</v>
@@ -7841,7 +7838,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B247" t="s">
         <v>260</v>
@@ -7893,7 +7890,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B249" t="s">
         <v>262</v>
@@ -7971,7 +7968,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B252" t="s">
         <v>265</v>
@@ -8023,7 +8020,7 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B254" t="s">
         <v>267</v>
